--- a/jpcore-r4/main/StructureDefinition-jp-observation-common.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-common.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1997" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2455" uniqueCount="513">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -329,16 +329,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -464,7 +464,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -614,13 +614,285 @@
     <t>どの観測値が取得されて表示されるかをフィルタリングするために使用されます。 / Used for filtering what observations are retrieved and displayed.</t>
   </si>
   <si>
+    <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:coding.system}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:first</t>
+  </si>
+  <si>
+    <t>first</t>
+  </si>
+  <si>
+    <t>検査の第1カテゴリはJP_SimpleObservationCategory_VSから値を指定する。</t>
+  </si>
+  <si>
+    <t>行われている一般的なタイプの観測を分類するコード。 / A code that classifies the general type of observation being made.</t>
+  </si>
+  <si>
+    <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
+    <t>Observation.category:first.id</t>
+  </si>
+  <si>
+    <t>Observation.category.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.category:first.extension</t>
+  </si>
+  <si>
+    <t>Observation.category.extension</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding</t>
+  </si>
+  <si>
+    <t>Observation.category.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>用語システムによって定義されたコード / Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>コードは、列挙されたCTなどの非常に正式な定義まで、列挙またはコードリストで非常にさりげなく定義される場合があります。詳細については、HL7 V3コアプリンシップを参照してください。コーディングの順序付けは未定義であり、意味を推測するために使用されません。一般に、せいぜい、コーディング値の1つのみがuserselected = trueとしてラベル付けされます。 / Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>コードシステム内の代替エンコーディング、および他のコードシステムへの翻訳が可能になります。 / Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.system</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.system</t>
+  </si>
+  <si>
+    <t>用語システムのアイデンティティ / Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>コード内のシンボルの意味を定義するコードシステムの識別。 / The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>uriは、oid（urn：oid：...）またはuuid（urn：uuid：...）である場合があります。OIDとUUIDは、HL7 OIDレジストリへの参照となります。それ以外の場合、URIは、FHIRの特別なURIを定義したHL7のリストから来るか、システムを明確かつ明確に確立する定義を参照する必要があります。 / The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.version</t>
+  </si>
+  <si>
+    <t>システムのバージョン - 関連する場合 / Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>このコードを選択するときに使用されたコードシステムのバージョン。コードの意味がバージョン全体で一貫しているため、適切にメンテナンスしたコードシステムでは報告されたバージョンを必要としないことに注意してください。ただし、これは一貫して保証することはできず、意味が一貫していることが保証されていない場合、バージョンを交換する必要があります。 / The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>用語がコードシステムバージョンを識別するために使用する文字列を明確に定義していない場合、推奨は、そのバージョンがバージョンの日付として公式に公開された日付（FHIR日付形式で表現）を使用することです。 / Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.code</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.code</t>
+  </si>
+  <si>
+    <t>システムによって定義された構文のシンボル / Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>システムによって定義された構文のシンボル。シンボルは、定義されたコードまたはコーディングシステムによって定義された構文の式（例：調整後）である場合があります。 / A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.display</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.display</t>
+  </si>
+  <si>
+    <t>システムによって定義された表現 / Representation defined by the system</t>
+  </si>
+  <si>
+    <t>システムのルールに従って、システム内のコードの意味の表現。 / A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>システムを知らない読者のために、コードの人間の読み取り可能な意味を持ち込むことができる必要があります。 / Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>このコーディングがユーザーによって直接選択された場合 / If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>このコーディングがユーザーによって直接選択されたことを示します。利用可能なアイテムのピックリスト（コードまたはディスプレイ）。 / Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>一連の代替案の中で、直接選択されたコードが新しい翻訳の最も適切な出発点です。この要素の使用とその結果をより完全に明確にするためには、「直接選択された」ことについては曖昧さがあり、取引パートナー契約が必要になる場合があります。 / Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>これは、臨床安全基準として特定されています - この正確なシステム/コードペアは、いくつかのルールまたは言語処理に基づいてシステムによって推測されるのではなく、明示的に選択されたことです。 / This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Observation.category:first.text</t>
+  </si>
+  <si>
+    <t>Observation.category.text</t>
+  </si>
+  <si>
+    <t>コンセプトの単純なテキスト表現 / Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>データを入力したユーザー、および/またはユーザーの意図された意味を表すユーザーによって見られる/選択/発言された概念の人間の言語表現。 / A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>多くの場合、テキストはコーディングの1つの表示名と同じです。 / Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>用語からのコードは、それらを使用する人間のすべてのニュアンスを使用して、常に正しい意味をキャプチャするとは限りません。または、適切なコードがまったくない場合があります。これらの場合、テキストはソースの完全な意味をキャプチャするために使用されます。 / The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -952,10 +1224,7 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -997,7 +1266,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common)
 </t>
   </si>
   <si>
@@ -1060,7 +1329,7 @@
     <t>どの値が「正常」と見なされるかを知ることは、特定の結果の意義を評価するのに役立つ。さまざまなコンテキストに対応するため複数の参照範囲を提供できる必要がある。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
@@ -1073,29 +1342,7 @@
     <t>Observation.referenceRange.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Observation.referenceRange.extension</t>
-  </si>
-  <si>
-    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Observation.referenceRange.modifierExtension</t>
@@ -1246,7 +1493,7 @@
     <t>このObservationに関連する子リソースに関する情報。このObservationに関連する/属するパネル検査や検査セットなどのObservationグループ</t>
   </si>
   <si>
-    <t>この要素を使用する場合、observationには通常、値または関連するリソースのセットのいじれかを含む。その両方を含む場合もある。複数のobservationをグループに一緒にまとめる方法については、以下の[メモ]（observation.html＃obsgrouping）を参照せよ。システムは、[QuestionnaireResponse]（questionnaireresponse.html）からの結果を計算して最終スコアにし、そのスコアをobservationとして表す場合があることに注意。</t>
+    <t>この要素を使用する場合、observationには通常、値または関連するリソースのセットのいずれかを含む。その両方を含む場合もある。複数のobservationをグループに一緒にまとめる方法については、以下の[メモ]（observation.html＃obsgrouping）を参照せよ。システムは、[QuestionnaireResponse]（questionnaireresponse.html）からの結果を計算して最終スコアにし、そのスコアをobservationとして表す場合があることに注意。</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
@@ -1674,7 +1921,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP51"/>
+  <dimension ref="A1:AP63"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
@@ -1705,7 +1952,7 @@
     <col min="26" max="26" width="63.09375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
@@ -3423,7 +3670,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>82</v>
@@ -3477,24 +3724,24 @@
       <c r="X15" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Y15" s="2"/>
+      <c r="Y15" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>83</v>
+        <v>195</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>187</v>
@@ -3521,10 +3768,10 @@
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>83</v>
@@ -3532,21 +3779,23 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="D16" t="s" s="2">
-        <v>196</v>
+        <v>83</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>94</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>83</v>
@@ -3555,22 +3804,22 @@
         <v>83</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>188</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>83</v>
@@ -3595,13 +3844,11 @@
         <v>83</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -3619,13 +3866,13 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>83</v>
@@ -3634,30 +3881,30 @@
         <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>203</v>
+        <v>83</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>204</v>
+        <v>83</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>205</v>
+        <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3677,23 +3924,19 @@
         <v>83</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>213</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>83</v>
       </c>
@@ -3753,22 +3996,22 @@
         <v>83</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>214</v>
+        <v>83</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>215</v>
+        <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>217</v>
+        <v>83</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>83</v>
@@ -3776,14 +4019,14 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3799,19 +4042,19 @@
         <v>83</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>219</v>
+        <v>140</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>220</v>
+        <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>221</v>
+        <v>143</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3849,19 +4092,19 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>83</v>
+        <v>195</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -3873,7 +4116,7 @@
         <v>83</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>83</v>
@@ -3882,13 +4125,13 @@
         <v>83</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>205</v>
+        <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>217</v>
+        <v>83</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>83</v>
@@ -3896,21 +4139,21 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>224</v>
+        <v>83</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>83</v>
@@ -3922,19 +4165,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -3983,13 +4226,13 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>83</v>
@@ -3998,19 +4241,19 @@
         <v>106</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>229</v>
+        <v>83</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>232</v>
+        <v>83</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>83</v>
@@ -4018,14 +4261,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>234</v>
+        <v>83</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4041,23 +4284,19 @@
         <v>83</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>235</v>
+        <v>206</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>83</v>
       </c>
@@ -4105,7 +4344,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4117,22 +4356,22 @@
         <v>83</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>239</v>
+        <v>83</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>240</v>
+        <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>241</v>
+        <v>210</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>242</v>
+        <v>83</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>83</v>
@@ -4140,21 +4379,21 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>83</v>
@@ -4163,19 +4402,19 @@
         <v>83</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>244</v>
+        <v>140</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>245</v>
+        <v>141</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>246</v>
+        <v>143</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4213,31 +4452,31 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>83</v>
+        <v>195</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>83</v>
@@ -4246,13 +4485,13 @@
         <v>83</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>247</v>
+        <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>248</v>
+        <v>210</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>249</v>
+        <v>83</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>83</v>
@@ -4260,10 +4499,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4271,10 +4510,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>83</v>
@@ -4286,26 +4525,26 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>251</v>
+        <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>83</v>
+        <v>237</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4347,13 +4586,13 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>83</v>
@@ -4362,19 +4601,19 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>255</v>
+        <v>83</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>258</v>
+        <v>83</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>83</v>
@@ -4382,10 +4621,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4408,20 +4647,18 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>83</v>
       </c>
@@ -4469,7 +4706,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4478,7 +4715,7 @@
         <v>94</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>264</v>
+        <v>83</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>106</v>
@@ -4487,27 +4724,27 @@
         <v>83</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>265</v>
+        <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>268</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4515,7 +4752,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>94</v>
@@ -4527,22 +4764,20 @@
         <v>83</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>188</v>
+        <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>271</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>272</v>
+        <v>253</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
@@ -4567,13 +4802,13 @@
         <v>83</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>273</v>
+        <v>83</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>274</v>
+        <v>83</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>275</v>
+        <v>83</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>83</v>
@@ -4591,7 +4826,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4600,7 +4835,7 @@
         <v>94</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>276</v>
+        <v>83</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>106</v>
@@ -4612,10 +4847,10 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>137</v>
+        <v>255</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -4626,21 +4861,21 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>278</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>279</v>
+        <v>83</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>83</v>
@@ -4649,22 +4884,20 @@
         <v>83</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>280</v>
+        <v>259</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>282</v>
+        <v>261</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -4689,13 +4922,13 @@
         <v>83</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>273</v>
+        <v>83</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>283</v>
+        <v>83</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>284</v>
+        <v>83</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>83</v>
@@ -4713,13 +4946,13 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>83</v>
@@ -4731,27 +4964,27 @@
         <v>83</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>285</v>
+        <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>289</v>
+        <v>266</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4762,7 +4995,7 @@
         <v>81</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>83</v>
@@ -4771,22 +5004,22 @@
         <v>83</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>290</v>
+        <v>267</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>291</v>
+        <v>268</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>292</v>
+        <v>270</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>293</v>
+        <v>271</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -4835,13 +5068,13 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>83</v>
@@ -4856,10 +5089,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>294</v>
+        <v>273</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>295</v>
+        <v>274</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -4870,10 +5103,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>296</v>
+        <v>275</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4893,21 +5126,23 @@
         <v>83</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>297</v>
+        <v>278</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
       </c>
@@ -4931,13 +5166,13 @@
         <v>83</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>299</v>
+        <v>83</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>83</v>
@@ -4955,7 +5190,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -4973,35 +5208,35 @@
         <v>83</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>83</v>
+        <v>285</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>94</v>
@@ -5013,22 +5248,22 @@
         <v>83</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
         <v>188</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5053,13 +5288,13 @@
         <v>83</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>200</v>
+        <v>289</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>309</v>
+        <v>290</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5077,10 +5312,10 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>94</v>
@@ -5092,30 +5327,30 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>83</v>
+        <v>292</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>83</v>
+        <v>293</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>83</v>
+        <v>297</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5135,21 +5370,23 @@
         <v>83</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>83</v>
       </c>
@@ -5197,7 +5434,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5212,30 +5449,30 @@
         <v>106</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>83</v>
+        <v>303</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>317</v>
+        <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>320</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5246,7 +5483,7 @@
         <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>83</v>
@@ -5255,19 +5492,19 @@
         <v>83</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5317,13 +5554,13 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>83</v>
@@ -5335,38 +5572,38 @@
         <v>83</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>325</v>
+        <v>83</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>326</v>
+        <v>294</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>328</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>83</v>
+        <v>313</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>83</v>
@@ -5375,22 +5612,22 @@
         <v>83</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>332</v>
+        <v>316</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5439,34 +5676,34 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>334</v>
+        <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>83</v>
+        <v>318</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>83</v>
+        <v>321</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>83</v>
@@ -5474,14 +5711,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>83</v>
+        <v>323</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5497,19 +5734,23 @@
         <v>83</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>83</v>
       </c>
@@ -5557,7 +5798,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>341</v>
+        <v>322</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5569,22 +5810,22 @@
         <v>83</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>83</v>
+        <v>328</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>83</v>
+        <v>329</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>83</v>
+        <v>331</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>83</v>
@@ -5592,21 +5833,21 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>83</v>
@@ -5615,19 +5856,19 @@
         <v>83</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>140</v>
+        <v>333</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>141</v>
+        <v>334</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>143</v>
+        <v>335</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5677,19 +5918,19 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>83</v>
@@ -5698,13 +5939,13 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>83</v>
+        <v>336</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>83</v>
+        <v>338</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>83</v>
@@ -5712,14 +5953,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>347</v>
+        <v>83</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5732,25 +5973,25 @@
         <v>83</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J34" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>140</v>
+        <v>340</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>143</v>
+        <v>342</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>149</v>
+        <v>343</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -5799,7 +6040,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5811,22 +6052,22 @@
         <v>83</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>83</v>
+        <v>344</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>83</v>
+        <v>345</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>137</v>
+        <v>346</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>83</v>
+        <v>347</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>83</v>
@@ -5834,10 +6075,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5857,19 +6098,23 @@
         <v>83</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="O35" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="L35" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>83</v>
       </c>
@@ -5917,7 +6162,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -5926,7 +6171,7 @@
         <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>106</v>
@@ -5935,19 +6180,19 @@
         <v>83</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>83</v>
+        <v>354</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP35" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="36">
@@ -5978,16 +6223,20 @@
         <v>83</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>352</v>
+        <v>188</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>359</v>
       </c>
       <c r="M36" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
@@ -6011,13 +6260,13 @@
         <v>83</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>83</v>
+        <v>362</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>83</v>
+        <v>363</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>83</v>
+        <v>364</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>83</v>
@@ -6044,7 +6293,7 @@
         <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>106</v>
@@ -6056,10 +6305,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>356</v>
+        <v>137</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6070,21 +6319,21 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>83</v>
+        <v>368</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>83</v>
@@ -6099,16 +6348,16 @@
         <v>188</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6133,37 +6382,37 @@
         <v>83</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>118</v>
+        <v>362</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="Z37" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>362</v>
-      </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>83</v>
@@ -6175,27 +6424,27 @@
         <v>83</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>287</v>
+        <v>376</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>83</v>
+        <v>377</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6218,19 +6467,19 @@
         <v>83</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>188</v>
+        <v>379</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6255,13 +6504,13 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>376</v>
+        <v>83</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>377</v>
+        <v>83</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -6279,7 +6528,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6297,13 +6546,13 @@
         <v>83</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>369</v>
+        <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>287</v>
+        <v>384</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6314,10 +6563,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6340,18 +6589,18 @@
         <v>83</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>379</v>
+        <v>188</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>83</v>
       </c>
@@ -6375,13 +6624,11 @@
         <v>83</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>83</v>
+        <v>388</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>83</v>
@@ -6399,7 +6646,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6417,27 +6664,27 @@
         <v>83</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>83</v>
+        <v>389</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>83</v>
+        <v>390</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>83</v>
+        <v>392</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6460,16 +6707,20 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>338</v>
+        <v>188</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
       </c>
@@ -6493,13 +6744,13 @@
         <v>83</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>83</v>
+        <v>289</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>83</v>
+        <v>397</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>83</v>
+        <v>398</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -6517,7 +6768,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6538,10 +6789,10 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>356</v>
+        <v>399</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>83</v>
@@ -6552,10 +6803,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6566,7 +6817,7 @@
         <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>83</v>
@@ -6575,19 +6826,19 @@
         <v>83</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6637,13 +6888,13 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>83</v>
@@ -6655,27 +6906,27 @@
         <v>83</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>83</v>
+        <v>405</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>83</v>
+        <v>408</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6686,7 +6937,7 @@
         <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>83</v>
@@ -6695,19 +6946,19 @@
         <v>83</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>395</v>
+        <v>410</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>396</v>
+        <v>411</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>396</v>
+        <v>411</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6757,13 +7008,13 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>83</v>
@@ -6775,27 +7026,27 @@
         <v>83</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>83</v>
+        <v>413</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>392</v>
+        <v>414</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>398</v>
+        <v>415</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>83</v>
+        <v>416</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6815,22 +7066,22 @@
         <v>83</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>330</v>
+        <v>418</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>400</v>
+        <v>419</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>400</v>
+        <v>419</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>401</v>
+        <v>420</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -6879,7 +7130,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -6891,7 +7142,7 @@
         <v>83</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>106</v>
+        <v>422</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>83</v>
@@ -6900,10 +7151,10 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -6914,10 +7165,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6940,13 +7191,13 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>338</v>
+        <v>206</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>339</v>
+        <v>207</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>340</v>
+        <v>208</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6997,7 +7248,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>341</v>
+        <v>209</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7021,7 +7272,7 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>342</v>
+        <v>210</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7032,10 +7283,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7064,7 +7315,7 @@
         <v>141</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>344</v>
+        <v>213</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>143</v>
@@ -7117,7 +7368,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>345</v>
+        <v>216</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7141,7 +7392,7 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>342</v>
+        <v>210</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7152,14 +7403,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>347</v>
+        <v>428</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7181,10 +7432,10 @@
         <v>140</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>348</v>
+        <v>429</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>349</v>
+        <v>430</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>143</v>
@@ -7239,7 +7490,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>350</v>
+        <v>431</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7274,10 +7525,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>408</v>
+        <v>432</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>408</v>
+        <v>432</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7285,7 +7536,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>94</v>
@@ -7297,23 +7548,19 @@
         <v>83</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>409</v>
+        <v>434</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
@@ -7337,13 +7584,13 @@
         <v>83</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>202</v>
+        <v>83</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>83</v>
@@ -7361,16 +7608,16 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>408</v>
+        <v>432</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>83</v>
+        <v>436</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7379,16 +7626,16 @@
         <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>412</v>
+        <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>205</v>
+        <v>437</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>206</v>
+        <v>438</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>83</v>
@@ -7396,10 +7643,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>413</v>
+        <v>439</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>413</v>
+        <v>439</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7419,23 +7666,19 @@
         <v>83</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>260</v>
+        <v>433</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>414</v>
+        <v>440</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>83</v>
       </c>
@@ -7483,7 +7726,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>413</v>
+        <v>439</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7492,7 +7735,7 @@
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>83</v>
+        <v>436</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -7501,27 +7744,27 @@
         <v>83</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>417</v>
+        <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>266</v>
+        <v>437</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>267</v>
+        <v>442</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>268</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>418</v>
+        <v>443</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>418</v>
+        <v>443</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7547,16 +7790,16 @@
         <v>188</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>419</v>
+        <v>444</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>420</v>
+        <v>445</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>421</v>
+        <v>446</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>272</v>
+        <v>447</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7581,13 +7824,13 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>273</v>
+        <v>118</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>274</v>
+        <v>448</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>275</v>
+        <v>449</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -7605,7 +7848,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>418</v>
+        <v>443</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7614,7 +7857,7 @@
         <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>276</v>
+        <v>83</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>106</v>
@@ -7623,13 +7866,13 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>83</v>
+        <v>450</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>137</v>
+        <v>451</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>277</v>
+        <v>376</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -7640,14 +7883,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>422</v>
+        <v>452</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>422</v>
+        <v>452</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>279</v>
+        <v>83</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7669,16 +7912,16 @@
         <v>188</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>423</v>
+        <v>453</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>424</v>
+        <v>454</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>425</v>
+        <v>455</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>426</v>
+        <v>456</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -7703,13 +7946,13 @@
         <v>83</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>283</v>
+        <v>457</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>284</v>
+        <v>458</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -7727,7 +7970,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>422</v>
+        <v>452</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7745,27 +7988,27 @@
         <v>83</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>285</v>
+        <v>450</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>286</v>
+        <v>451</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>287</v>
+        <v>376</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>427</v>
+        <v>459</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>427</v>
+        <v>459</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7776,7 +8019,7 @@
         <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>83</v>
@@ -7788,19 +8031,17 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>84</v>
+        <v>460</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>428</v>
+        <v>461</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>430</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>431</v>
+        <v>463</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -7849,13 +8090,13 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>427</v>
+        <v>459</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>83</v>
@@ -7870,15 +8111,1465 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>335</v>
+        <v>83</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>336</v>
+        <v>464</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP52" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP53" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP54" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="P55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP56" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP57" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP58" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="P60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP63" t="s" s="2">
         <v>83</v>
       </c>
     </row>

--- a/jpcore-r4/main/StructureDefinition-jp-observation-common.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-common.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-observation-common.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-common.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2455" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2456" uniqueCount="514">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReasonは、Observation.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:Observation.codeがObservation.component.codeと同じ場合、そのcodeに関連付くvalueは存在してはならない。 / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1143,7 +1143,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>結果（ `balue.value [x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
+    <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
@@ -1224,7 +1224,10 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
+    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1330,7 +1333,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
+obs-3:少なくともlow, high, textのいずれかが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
     <t>OBX.7</t>
@@ -1401,7 +1404,7 @@
     <t>Observation.referenceRange.type</t>
   </si>
   <si>
-    <t>参照範囲予選 / Reference range qualifier</t>
+    <t>参照範囲予選修飾子 / Reference range qualifier</t>
   </si>
   <si>
     <t>適用されるターゲット参照母集団のどの部分を示すコード。たとえば、通常または治療範囲。 / Codes to indicate the what part of the targeted reference population it applies to. For example, the normal or therapeutic range.</t>
@@ -1586,7 +1589,7 @@
   </si>
   <si>
     <t>「null」または例外的な値は、FHIR観測で2つの方法を表すことができます。1つの方法は、それらを単に値セットに含めるだけで、値の例外を表すことです。たとえば、血清学テストの測定値は、「検出」、「検出されない」、「決定的でない」、または「テストなし」です。
-別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、DataBsentrasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
+別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、dataAbsentReasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
 The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
   </si>
   <si>
@@ -1948,7 +1951,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="105.8828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="63.09375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -6626,9 +6629,11 @@
       <c r="X39" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="Y39" s="2"/>
+      <c r="Y39" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>83</v>
@@ -6664,27 +6669,27 @@
         <v>83</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6710,16 +6715,16 @@
         <v>188</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6747,10 +6752,10 @@
         <v>289</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -6768,7 +6773,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6789,10 +6794,10 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>83</v>
@@ -6803,10 +6808,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6829,16 +6834,16 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6888,7 +6893,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6906,27 +6911,27 @@
         <v>83</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6949,16 +6954,16 @@
         <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7008,7 +7013,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7026,27 +7031,27 @@
         <v>83</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7069,19 +7074,19 @@
         <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7130,7 +7135,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7142,7 +7147,7 @@
         <v>83</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>83</v>
@@ -7151,10 +7156,10 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7165,10 +7170,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7283,10 +7288,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7403,14 +7408,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7432,10 +7437,10 @@
         <v>140</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>143</v>
@@ -7490,7 +7495,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7525,10 +7530,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7551,13 +7556,13 @@
         <v>83</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7608,7 +7613,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7617,7 +7622,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7629,10 +7634,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7643,10 +7648,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7669,13 +7674,13 @@
         <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7726,7 +7731,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7735,7 +7740,7 @@
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -7747,10 +7752,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7761,10 +7766,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7790,16 +7795,16 @@
         <v>188</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7827,10 +7832,10 @@
         <v>118</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -7848,7 +7853,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7866,10 +7871,10 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>376</v>
@@ -7883,10 +7888,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7912,16 +7917,16 @@
         <v>188</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -7949,10 +7954,10 @@
         <v>289</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -7970,7 +7975,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7988,10 +7993,10 @@
         <v>83</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>376</v>
@@ -8005,10 +8010,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8031,17 +8036,17 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8090,7 +8095,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8114,7 +8119,7 @@
         <v>83</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8125,10 +8130,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8154,10 +8159,10 @@
         <v>206</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8208,7 +8213,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8229,10 +8234,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8243,10 +8248,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8269,16 +8274,16 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8328,7 +8333,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8349,10 +8354,10 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8363,10 +8368,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8389,16 +8394,16 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8448,7 +8453,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8469,10 +8474,10 @@
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8483,10 +8488,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8509,19 +8514,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8570,7 +8575,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8591,10 +8596,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8605,10 +8610,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8723,10 +8728,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8843,14 +8848,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8872,10 +8877,10 @@
         <v>140</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>143</v>
@@ -8930,7 +8935,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8965,10 +8970,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8994,13 +8999,13 @@
         <v>188</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O59" t="s" s="2">
         <v>288</v>
@@ -9052,7 +9057,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>94</v>
@@ -9070,7 +9075,7 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>294</v>
@@ -9087,10 +9092,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9116,13 +9121,13 @@
         <v>349</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O60" t="s" s="2">
         <v>352</v>
@@ -9174,7 +9179,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9192,7 +9197,7 @@
         <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>355</v>
@@ -9209,10 +9214,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9238,13 +9243,13 @@
         <v>188</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="O61" t="s" s="2">
         <v>361</v>
@@ -9296,7 +9301,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9331,10 +9336,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9360,16 +9365,16 @@
         <v>188</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9418,7 +9423,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9453,10 +9458,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9482,16 +9487,16 @@
         <v>84</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9540,7 +9545,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9561,10 +9566,10 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/main/StructureDefinition-jp-observation-common.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-common.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/main/StructureDefinition-jp-observation-common.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-common.xlsx
@@ -1927,15 +1927,15 @@
   <dimension ref="A1:AP63"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="38.30078125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1946,28 +1946,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.09375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="95.48828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.09375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/main/StructureDefinition-jp-observation-common.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-common.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/main/StructureDefinition-jp-observation-common.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-common.xlsx
@@ -383,7 +383,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -617,7 +617,7 @@
     <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -917,7 +917,7 @@
     <t>単純な観測の名前を識別するコード。 / Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -969,7 +969,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1146,7 +1146,7 @@
     <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1175,7 +1175,7 @@
     <t>観測の解釈を識別するコード。 / Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1227,7 +1227,7 @@
     <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1257,7 +1257,7 @@
     <t>単純な観測の方法。 / Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1294,7 +1294,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1369,7 +1369,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1419,7 +1419,7 @@
     <t>参照範囲の意味のコード。 / Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1452,7 +1452,7 @@
     <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>

--- a/jpcore-r4/main/StructureDefinition-jp-observation-common.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-common.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
